--- a/docs/evidencias-testes/evidencia_ lotes.xlsx
+++ b/docs/evidencias-testes/evidencia_ lotes.xlsx
@@ -110,16 +110,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>2002</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>lote-1mb.zip</t>
+          <t>lote-1mb_09102026180828.zip</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fa629ad5cfbc8b6846b958dd7ee87b4834306a39f6ef45644fb26cf7f400b44a</t>
+          <t>b95a6501bad765982f45de1925c364b6d2459ee1c46d0bcd4b3b58e2ab508832</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -131,81 +131,81 @@
         <v>6</v>
       </c>
       <c r="G2" s="3">
-        <v>46302.947234762454</v>
+        <v>46304.88134209035</v>
       </c>
       <c r="H2" s="3">
-        <v>46303.07627097126</v>
+        <v>46304.881374025186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>2</v>
+        <v>2003</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lote-valido.zip</t>
+          <t>lote-corrompido_09102026180828.zip</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>a953ee3ee9903962925b756f39081a6327ea82c85599093d6383523c588ce5d6</t>
+          <t>a9facae0e5a464fd6eed77f9496c34b48c060034a12890f15d72bb502cd3f408</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CONCLUIDO</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>7</v>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Arquivo ZIP corrompido ou inválido</t>
+        </is>
       </c>
       <c r="G3" s="3">
-        <v>46304.06796066399</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46304.068028085836</v>
+        <v>46304.88143928647</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>3</v>
+        <v>2004</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lote-corrompido.zip</t>
+          <t>lote-com-arquivos-nao-processaveis_09102026180828.zip</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>90c94b0461ba0499843b097f9e8405cea810e6ed4ef4d60d1e848bf6390d433e</t>
+          <t>8f9ed8878e1607f0c5e5bed7deaabbd68396b48565d30fb4f94abd2c176778e2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Arquivo ZIP corrompido ou inválido</t>
-        </is>
+          <t>CONCLUIDO</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>6</v>
       </c>
       <c r="G4" s="3">
-        <v>46304.08016034783</v>
+        <v>46304.88156051367</v>
+      </c>
+      <c r="H4" s="3">
+        <v>46304.88156698712</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>4</v>
+        <v>2005</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lote-com-erros.zip</t>
+          <t>lote-com-erros_09102026180828.zip</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>a6c232af1c9f552840ea458594ba39ec6eb4cfc1b3fb27f555d1ae9123360bee</t>
+          <t>32f75908154ffafd4b4fa14c48d341763edb190cd32499dd6dadfddaf3c510bd</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -217,24 +217,24 @@
         <v>10</v>
       </c>
       <c r="G5" s="3">
-        <v>46304.080613147926</v>
+        <v>46304.881662235886</v>
       </c>
       <c r="H5" s="3">
-        <v>46304.080644865826</v>
+        <v>46304.88166945324</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5</v>
+        <v>2006</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lote-com-arquivos-nao-processaveis.zip</t>
+          <t>lote-valido_09102026180828.zip</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1634d6d5eda5c69db965379a2f671cf728f65ef56198c825c24ffb3154a944a5</t>
+          <t>2f3ac4db00e73ca55a94908870da7e4deadf945bbb30dd575f6f7d8389bf3799</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -243,100 +243,13 @@
         </is>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="3">
-        <v>46304.08314470319</v>
+        <v>46304.88181975758</v>
       </c>
       <c r="H6" s="3">
-        <v>46304.08315964191</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>lote-1mb - 2.zip</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2b87679a86345ad24798c56a50324fda5d893d6705798ae57e73c3777ef1679b</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CONCLUIDO</t>
-        </is>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="G7" s="3">
-        <v>46304.09171245084</v>
-      </c>
-      <c r="H7" s="3">
-        <v>46304.0917779919</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>1002</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>lote-1mb_09102026135016.zip</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ada90f5cbcc38e2b5deabce72a8a7e4b1dfaf30a8aea264bed97ba87eca1225d</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CONCLUIDO</t>
-        </is>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="G8" s="3">
-        <v>46304.703681600855</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46304.70372052561</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>1003</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lote-valido_09102026164534.zip</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>cc5699d04f5d0019666606cb382b2b4620f6de1ae22d5100193f5fadef98ddcc</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CONCLUIDO</t>
-        </is>
-      </c>
-      <c r="E9">
-        <v>7</v>
-      </c>
-      <c r="G9" s="3">
-        <v>46304.71153669288</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46304.73345035911</v>
+        <v>46304.88182671822</v>
       </c>
     </row>
   </sheetData>
